--- a/engineering/MAP_V2/00_Architecture/Verification/Phase_08/Phase_08_Table_Inventory.xlsx
+++ b/engineering/MAP_V2/00_Architecture/Verification/Phase_08/Phase_08_Table_Inventory.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Table Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Action Required" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Rejected Tables" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Required" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected Tables" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table Inventory'!$A$1:$M$45</definedName>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +41,17 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C62828"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -79,8 +88,38 @@
         <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E65100"/>
+        <bgColor rgb="00E65100"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C62828"/>
+        <bgColor rgb="00C62828"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+        <bgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBEE"/>
+        <bgColor rgb="00FFEBEE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -94,11 +133,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -118,6 +185,28 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,22 +572,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="38" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="52" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="62" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,6 +658,16 @@
           <t>Solution</t>
         </is>
       </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Evidence ID</t>
+        </is>
+      </c>
+      <c r="O1" s="8" t="inlineStr">
+        <is>
+          <t>Rule 19 Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -574,6 +675,20 @@
           <t>Dashboard Feature</t>
         </is>
       </c>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
+      <c r="G2" s="9" t="n"/>
+      <c r="H2" s="9" t="n"/>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="9" t="n"/>
+      <c r="K2" s="9" t="n"/>
+      <c r="L2" s="9" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -639,6 +754,16 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>DL-002</t>
+        </is>
+      </c>
+      <c r="O3" s="11" t="inlineStr">
+        <is>
+          <t>VERIFIED — uses authoritative MAP CLI tables</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -704,6 +829,16 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>DL-002</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>VERIFIED — uses authoritative MAP CLI tables</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -769,6 +904,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -834,6 +971,16 @@
           <t>Replace audit.audit_events with engine.migration_control_execution. Map: action-&gt;execution_status, entity_type-&gt;control_id, entity_id-&gt;rule_id, user_email-&gt;SYSTEM, timestamp-&gt;created_at</t>
         </is>
       </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>DL-007</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — Phase 08: replaced engine.audit_log with engine.migration_control_execution</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -841,6 +988,20 @@
           <t>Governance Feature</t>
         </is>
       </c>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -906,6 +1067,16 @@
           <t>Replace engine.audit_log with engine.migration_control_execution. Map: action-&gt;execution_status, entity_type-&gt;control_id, entity_id-&gt;rule_id, user_email-&gt;SYSTEM, timestamp-&gt;created_at</t>
         </is>
       </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>DL-007</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — Phase 08: replaced engine.audit_log with engine.migration_control_execution</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -971,6 +1142,16 @@
           <t>Replace engine.approvals with engine.migration_release_decision. Map: status-&gt;gate_result, requested_by-&gt;approved_by, entity_type-&gt;client_name, entity_id-&gt;batch_id</t>
         </is>
       </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>DL-010</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>VERIFIED — Phase 08: replaced engine.approvals with engine.migration_release_decision</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1036,6 +1217,16 @@
           <t>Replace engine.exceptions with engine.migration_control_exceptions. Map: reason-&gt;cause, status-&gt;failure_scope, requested_by-&gt;SYSTEM, entity_type-&gt;control_id, entity_id-&gt;rule_id</t>
         </is>
       </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>DL-009</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — Phase 08: replaced engine.exceptions with engine.migration_control_exceptions</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1043,6 +1234,20 @@
           <t>Execution Control Feature</t>
         </is>
       </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1108,6 +1313,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1173,6 +1380,16 @@
           <t>Option A (Partial): Use batch_execution_checkpoint - frontend adapts to checkpoint data. Option B (Full): Create engine.migration_batch_lifecycle table + add INSERT to execution_engine.py</t>
         </is>
       </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>DL-005</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>PARTIAL — engine.migration_batch_lifecycle does not exist; uses engine.batch_execution_checkpoint (batch_id + last_completed_control only)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1238,6 +1455,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1245,6 +1464,20 @@
           <t>Execution History Feature</t>
         </is>
       </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1310,6 +1543,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1375,6 +1610,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1440,6 +1677,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1505,6 +1744,16 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>DL-009</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — Phase 08: replaced engine.exceptions with engine.migration_control_exceptions</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1570,6 +1819,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1577,6 +1828,20 @@
           <t>Validation Report Feature</t>
         </is>
       </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="10" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1642,6 +1907,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1707,6 +1974,16 @@
           <t>Option A: Trace population source, adapt mapping: risk_score-&gt;final_score, risk_level-&gt;computed, calculated_timestamp-&gt;created_at. Option B: If source untraceable, BLOCK per RULE 16</t>
         </is>
       </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>DL-001</t>
+        </is>
+      </c>
+      <c r="O23" s="13" t="inlineStr">
+        <is>
+          <t>DEPRECATED — engine.unified_scores has no Python INSERT, no MAP CLI writer. Replaced during Phase 08.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1772,6 +2049,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N24" s="3" t="n"/>
+      <c r="O24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1837,6 +2116,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1902,6 +2183,16 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>DL-009</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="inlineStr">
+        <is>
+          <t>FIXED — Phase 08: replaced engine.exceptions with engine.migration_control_exceptions</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1967,6 +2258,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1974,6 +2267,20 @@
           <t>Rule Execution Feature</t>
         </is>
       </c>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="9" t="n"/>
+      <c r="I28" s="9" t="n"/>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
+      <c r="L28" s="9" t="n"/>
+      <c r="M28" s="10" t="n"/>
+      <c r="N28" s="3" t="n"/>
+      <c r="O28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -2039,6 +2346,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N29" s="3" t="n"/>
+      <c r="O29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -2104,6 +2413,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N30" s="3" t="n"/>
+      <c r="O30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -2169,6 +2480,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N31" s="3" t="n"/>
+      <c r="O31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2176,6 +2489,20 @@
           <t>Monitoring Feature</t>
         </is>
       </c>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="9" t="n"/>
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="3" t="n"/>
+      <c r="O32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -2241,6 +2568,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2248,6 +2577,20 @@
           <t>Discovery Feature</t>
         </is>
       </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="9" t="n"/>
+      <c r="M34" s="10" t="n"/>
+      <c r="N34" s="3" t="n"/>
+      <c r="O34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -2313,6 +2656,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2378,6 +2723,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N36" s="3" t="n"/>
+      <c r="O36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2385,6 +2732,20 @@
           <t>Platform Features</t>
         </is>
       </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="10" t="n"/>
+      <c r="N37" s="3" t="n"/>
+      <c r="O37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2450,6 +2811,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N38" s="3" t="n"/>
+      <c r="O38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2515,6 +2878,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2580,6 +2945,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N40" s="3" t="n"/>
+      <c r="O40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2645,6 +3012,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N41" s="3" t="n"/>
+      <c r="O41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2710,6 +3079,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N42" s="3" t="n"/>
+      <c r="O42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2775,6 +3146,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N43" s="3" t="n"/>
+      <c r="O43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2840,6 +3213,8 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N44" s="3" t="n"/>
+      <c r="O44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2905,13 +3280,315 @@
           <t>No change needed</t>
         </is>
       </c>
+      <c r="N45" s="3" t="n"/>
+      <c r="O45" s="3" t="n"/>
+    </row>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>RULE 19 — PROHIBITED TABLE NAMES</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>engine.audit_log</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="n"/>
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="16" t="n"/>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>engine.migration_control_execution</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="n"/>
+      <c r="G49" s="16" t="n"/>
+      <c r="H49" s="16" t="n"/>
+      <c r="I49" s="16" t="n"/>
+      <c r="J49" s="16" t="n"/>
+      <c r="K49" s="16" t="n"/>
+      <c r="L49" s="16" t="n"/>
+      <c r="M49" s="16" t="n"/>
+      <c r="N49" s="16" t="n"/>
+      <c r="O49" s="16" t="inlineStr">
+        <is>
+          <t>FIXED — Phase 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>engine.approvals</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="n"/>
+      <c r="C50" s="16" t="n"/>
+      <c r="D50" s="16" t="n"/>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>engine.migration_release_decision</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="n"/>
+      <c r="G50" s="16" t="n"/>
+      <c r="H50" s="16" t="n"/>
+      <c r="I50" s="16" t="n"/>
+      <c r="J50" s="16" t="n"/>
+      <c r="K50" s="16" t="n"/>
+      <c r="L50" s="16" t="n"/>
+      <c r="M50" s="16" t="n"/>
+      <c r="N50" s="16" t="n"/>
+      <c r="O50" s="16" t="inlineStr">
+        <is>
+          <t>VERIFIED — Phase 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>engine.exceptions</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="n"/>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="n"/>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>engine.migration_control_exceptions</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="n"/>
+      <c r="G51" s="16" t="n"/>
+      <c r="H51" s="16" t="n"/>
+      <c r="I51" s="16" t="n"/>
+      <c r="J51" s="16" t="n"/>
+      <c r="K51" s="16" t="n"/>
+      <c r="L51" s="16" t="n"/>
+      <c r="M51" s="16" t="n"/>
+      <c r="N51" s="16" t="n"/>
+      <c r="O51" s="16" t="inlineStr">
+        <is>
+          <t>FIXED — Phase 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>engine.systems</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="n"/>
+      <c r="C52" s="16" t="n"/>
+      <c r="D52" s="16" t="n"/>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>core.system_registry</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="n"/>
+      <c r="G52" s="16" t="n"/>
+      <c r="H52" s="16" t="n"/>
+      <c r="I52" s="16" t="n"/>
+      <c r="J52" s="16" t="n"/>
+      <c r="K52" s="16" t="n"/>
+      <c r="L52" s="16" t="n"/>
+      <c r="M52" s="16" t="n"/>
+      <c r="N52" s="16" t="n"/>
+      <c r="O52" s="16" t="inlineStr">
+        <is>
+          <t>VERIFIED — Phase 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>engine.controls</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="n"/>
+      <c r="C53" s="16" t="n"/>
+      <c r="D53" s="16" t="n"/>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>engine.control_registry</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="n"/>
+      <c r="G53" s="16" t="n"/>
+      <c r="H53" s="16" t="n"/>
+      <c r="I53" s="16" t="n"/>
+      <c r="J53" s="16" t="n"/>
+      <c r="K53" s="16" t="n"/>
+      <c r="L53" s="16" t="n"/>
+      <c r="M53" s="16" t="n"/>
+      <c r="N53" s="16" t="n"/>
+      <c r="O53" s="16" t="inlineStr">
+        <is>
+          <t>VERIFIED — Phase 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>engine.migration_batch_lifecycle</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="n"/>
+      <c r="C54" s="16" t="n"/>
+      <c r="D54" s="16" t="n"/>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>engine.batch_execution_checkpoint (partial)</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="n"/>
+      <c r="G54" s="16" t="n"/>
+      <c r="H54" s="16" t="n"/>
+      <c r="I54" s="16" t="n"/>
+      <c r="J54" s="16" t="n"/>
+      <c r="K54" s="16" t="n"/>
+      <c r="L54" s="16" t="n"/>
+      <c r="M54" s="16" t="n"/>
+      <c r="N54" s="16" t="n"/>
+      <c r="O54" s="16" t="inlineStr">
+        <is>
+          <t>DOCUMENTED — Phase 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>engine.migration_risk_scores</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="n"/>
+      <c r="C55" s="16" t="n"/>
+      <c r="D55" s="16" t="n"/>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>Authoritative view pending runtime verification</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="16" t="n"/>
+      <c r="H55" s="16" t="n"/>
+      <c r="I55" s="16" t="n"/>
+      <c r="J55" s="16" t="n"/>
+      <c r="K55" s="16" t="n"/>
+      <c r="L55" s="16" t="n"/>
+      <c r="M55" s="16" t="n"/>
+      <c r="N55" s="16" t="n"/>
+      <c r="O55" s="16" t="inlineStr">
+        <is>
+          <t>BLOCKED — DDL never executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>engine.unified_scores</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="n"/>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>Authoritative source pending Stage 3/4 verification</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="16" t="n"/>
+      <c r="H56" s="16" t="n"/>
+      <c r="I56" s="16" t="n"/>
+      <c r="J56" s="16" t="n"/>
+      <c r="K56" s="16" t="n"/>
+      <c r="L56" s="16" t="n"/>
+      <c r="M56" s="16" t="n"/>
+      <c r="N56" s="16" t="n"/>
+      <c r="O56" s="16" t="inlineStr">
+        <is>
+          <t>DEPRECATED — no Python INSERT, no MAP CLI writer</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>audit.audit_events</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="n"/>
+      <c r="C57" s="16" t="n"/>
+      <c r="D57" s="16" t="n"/>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>engine.migration_control_execution</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="n"/>
+      <c r="G57" s="16" t="n"/>
+      <c r="H57" s="16" t="n"/>
+      <c r="I57" s="16" t="n"/>
+      <c r="J57" s="16" t="n"/>
+      <c r="K57" s="16" t="n"/>
+      <c r="L57" s="16" t="n"/>
+      <c r="M57" s="16" t="n"/>
+      <c r="N57" s="16" t="n"/>
+      <c r="O57" s="16" t="inlineStr">
+        <is>
+          <t>FIXED — Phase 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>platform.approval_requests</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="n"/>
+      <c r="C58" s="16" t="n"/>
+      <c r="D58" s="16" t="n"/>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>engine.migration_release_decision</t>
+        </is>
+      </c>
+      <c r="F58" s="16" t="n"/>
+      <c r="G58" s="16" t="n"/>
+      <c r="H58" s="16" t="n"/>
+      <c r="I58" s="16" t="n"/>
+      <c r="J58" s="16" t="n"/>
+      <c r="K58" s="16" t="n"/>
+      <c r="L58" s="16" t="n"/>
+      <c r="M58" s="16" t="n"/>
+      <c r="N58" s="16" t="n"/>
+      <c r="O58" s="16" t="inlineStr">
+        <is>
+          <t>DOCUMENTED — 0 rows, no MAP CLI writer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M45"/>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A37:M37"/>
     <mergeCell ref="A32:M32"/>
     <mergeCell ref="A34:M34"/>
+    <mergeCell ref="A48:M48"/>
     <mergeCell ref="A21:M21"/>
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A7:M7"/>
